--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285103</v>
+        <v>134285122</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425095</v>
+        <v>425710</v>
       </c>
       <c r="R20" t="n">
-        <v>7024364</v>
+        <v>7024267</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,11 +2560,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134285122</v>
+        <v>134285103</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,21 +2597,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425710</v>
+        <v>425095</v>
       </c>
       <c r="R21" t="n">
-        <v>7024267</v>
+        <v>7024364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,6 +2657,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,10 +3002,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134285084</v>
+        <v>134285120</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425496</v>
+        <v>425614</v>
       </c>
       <c r="R25" t="n">
-        <v>7024347</v>
+        <v>7024375</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,11 +3073,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3104,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134285120</v>
+        <v>134285084</v>
       </c>
       <c r="B26" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,21 +3110,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3139,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425614</v>
+        <v>425496</v>
       </c>
       <c r="R26" t="n">
-        <v>7024375</v>
+        <v>7024347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3175,6 +3170,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3201,32 +3201,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285089</v>
+        <v>134285113</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>92392</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425778</v>
+        <v>425631</v>
       </c>
       <c r="R27" t="n">
-        <v>7024318</v>
+        <v>7024062</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,11 +3272,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3303,32 +3298,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134285113</v>
+        <v>134285089</v>
       </c>
       <c r="B28" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425631</v>
+        <v>425778</v>
       </c>
       <c r="R28" t="n">
-        <v>7024062</v>
+        <v>7024318</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3374,6 +3369,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285082</v>
+        <v>134285085</v>
       </c>
       <c r="B31" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425684</v>
+        <v>425469</v>
       </c>
       <c r="R31" t="n">
-        <v>7024370</v>
+        <v>7024326</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3665,6 +3665,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3691,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134285121</v>
+        <v>134285082</v>
       </c>
       <c r="B32" t="n">
-        <v>91956</v>
+        <v>91960</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3702,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3726,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425149</v>
+        <v>425684</v>
       </c>
       <c r="R32" t="n">
-        <v>7024338</v>
+        <v>7024370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134285085</v>
+        <v>134285121</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3804,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3828,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425469</v>
+        <v>425149</v>
       </c>
       <c r="R33" t="n">
-        <v>7024326</v>
+        <v>7024338</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,11 +3864,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,32 +4094,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285125</v>
+        <v>134285124</v>
       </c>
       <c r="B36" t="n">
-        <v>92675</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425669</v>
+        <v>425174</v>
       </c>
       <c r="R36" t="n">
-        <v>7024226</v>
+        <v>7024293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4191,32 +4191,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285124</v>
+        <v>134285125</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>92675</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425174</v>
+        <v>425669</v>
       </c>
       <c r="R37" t="n">
-        <v>7024293</v>
+        <v>7024226</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134285101</v>
+        <v>134285086</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -704,16 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425161</v>
+        <v>425545</v>
       </c>
       <c r="R2" t="n">
-        <v>7024570</v>
+        <v>7024309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285086</v>
+        <v>134285101</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -806,24 +814,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425545</v>
+        <v>425161</v>
       </c>
       <c r="R3" t="n">
-        <v>7024309</v>
+        <v>7024570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134285112</v>
+        <v>134285090</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,16 +1000,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425364</v>
+        <v>425660</v>
       </c>
       <c r="R5" t="n">
-        <v>7024553</v>
+        <v>7024220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285087</v>
+        <v>134285112</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,16 +1102,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425580</v>
+        <v>425364</v>
       </c>
       <c r="R6" t="n">
-        <v>7024207</v>
+        <v>7024553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285090</v>
+        <v>134285087</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425660</v>
+        <v>425580</v>
       </c>
       <c r="R7" t="n">
-        <v>7024220</v>
+        <v>7024207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,32 +1295,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285114</v>
+        <v>134285093</v>
       </c>
       <c r="B8" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425779</v>
+        <v>425665</v>
       </c>
       <c r="R8" t="n">
-        <v>7024201</v>
+        <v>7024266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,32 +1397,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285093</v>
+        <v>134285114</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425665</v>
+        <v>425779</v>
       </c>
       <c r="R9" t="n">
-        <v>7024266</v>
+        <v>7024201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,7 +1701,7 @@
         <v>134285118</v>
       </c>
       <c r="B12" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>134285115</v>
       </c>
       <c r="B13" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>134285116</v>
       </c>
       <c r="B14" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>134285123</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,32 +2086,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285111</v>
+        <v>134285097</v>
       </c>
       <c r="B16" t="n">
-        <v>99203</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425183</v>
+        <v>425427</v>
       </c>
       <c r="R16" t="n">
-        <v>7024304</v>
+        <v>7024497</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2157,6 +2157,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,32 +2188,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285097</v>
+        <v>134285111</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>99210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425427</v>
+        <v>425183</v>
       </c>
       <c r="R17" t="n">
-        <v>7024497</v>
+        <v>7024304</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2254,11 +2259,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285095</v>
+        <v>134285083</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425676</v>
+        <v>425428</v>
       </c>
       <c r="R18" t="n">
-        <v>7024309</v>
+        <v>7024294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285083</v>
+        <v>134285095</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425428</v>
+        <v>425676</v>
       </c>
       <c r="R19" t="n">
-        <v>7024294</v>
+        <v>7024309</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285122</v>
+        <v>134285103</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425710</v>
+        <v>425095</v>
       </c>
       <c r="R20" t="n">
-        <v>7024267</v>
+        <v>7024364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,6 +2560,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,7 +2591,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134285103</v>
+        <v>134285094</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425095</v>
+        <v>425647</v>
       </c>
       <c r="R21" t="n">
-        <v>7024364</v>
+        <v>7024281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,10 +2693,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134285094</v>
+        <v>134285122</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2699,21 +2704,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425647</v>
+        <v>425710</v>
       </c>
       <c r="R22" t="n">
-        <v>7024281</v>
+        <v>7024267</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,11 +2764,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,7 +3005,7 @@
         <v>134285120</v>
       </c>
       <c r="B25" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,32 +3201,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285113</v>
+        <v>134285089</v>
       </c>
       <c r="B27" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425631</v>
+        <v>425778</v>
       </c>
       <c r="R27" t="n">
-        <v>7024062</v>
+        <v>7024318</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,6 +3272,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3298,32 +3303,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134285089</v>
+        <v>134285113</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3333,10 +3338,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425778</v>
+        <v>425631</v>
       </c>
       <c r="R28" t="n">
-        <v>7024318</v>
+        <v>7024062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3369,11 +3374,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134285117</v>
+        <v>134285119</v>
       </c>
       <c r="B29" t="n">
-        <v>92231</v>
+        <v>91963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425689</v>
+        <v>425723</v>
       </c>
       <c r="R29" t="n">
-        <v>7024137</v>
+        <v>7024299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134285119</v>
+        <v>134285117</v>
       </c>
       <c r="B30" t="n">
-        <v>91956</v>
+        <v>92238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425723</v>
+        <v>425689</v>
       </c>
       <c r="R30" t="n">
-        <v>7024299</v>
+        <v>7024137</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285085</v>
+        <v>134285121</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>91963</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425469</v>
+        <v>425149</v>
       </c>
       <c r="R31" t="n">
-        <v>7024326</v>
+        <v>7024338</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3665,11 +3665,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3699,7 +3694,7 @@
         <v>134285082</v>
       </c>
       <c r="B32" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134285121</v>
+        <v>134285085</v>
       </c>
       <c r="B33" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3804,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3828,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425149</v>
+        <v>425469</v>
       </c>
       <c r="R33" t="n">
-        <v>7024338</v>
+        <v>7024326</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3864,6 +3859,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,32 +4094,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285124</v>
+        <v>134285125</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>92682</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425174</v>
+        <v>425669</v>
       </c>
       <c r="R36" t="n">
-        <v>7024293</v>
+        <v>7024226</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4191,32 +4191,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285125</v>
+        <v>134285124</v>
       </c>
       <c r="B37" t="n">
-        <v>92675</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425669</v>
+        <v>425174</v>
       </c>
       <c r="R37" t="n">
-        <v>7024226</v>
+        <v>7024293</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134285086</v>
+        <v>134285117</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425545</v>
+        <v>425689</v>
       </c>
       <c r="R2" t="n">
-        <v>7024309</v>
+        <v>7024137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285101</v>
+        <v>134285118</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425161</v>
+        <v>425175</v>
       </c>
       <c r="R3" t="n">
-        <v>7024570</v>
+        <v>7024293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134285098</v>
+        <v>134285125</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>92689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425419</v>
+        <v>425669</v>
       </c>
       <c r="R4" t="n">
-        <v>7024500</v>
+        <v>7024226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134285090</v>
+        <v>134285119</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425660</v>
+        <v>425723</v>
       </c>
       <c r="R5" t="n">
-        <v>7024220</v>
+        <v>7024299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285112</v>
+        <v>134285120</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425364</v>
+        <v>425614</v>
       </c>
       <c r="R6" t="n">
-        <v>7024553</v>
+        <v>7024375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285087</v>
+        <v>134285121</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425580</v>
+        <v>425149</v>
       </c>
       <c r="R7" t="n">
-        <v>7024207</v>
+        <v>7024338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285093</v>
+        <v>134285082</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425665</v>
+        <v>425684</v>
       </c>
       <c r="R8" t="n">
-        <v>7024266</v>
+        <v>7024370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285114</v>
+        <v>134285113</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1432,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425779</v>
+        <v>425631</v>
       </c>
       <c r="R9" t="n">
-        <v>7024201</v>
+        <v>7024062</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134285100</v>
+        <v>134285114</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>92406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425316</v>
+        <v>425779</v>
       </c>
       <c r="R10" t="n">
-        <v>7024560</v>
+        <v>7024201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134285088</v>
+        <v>134285115</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>92406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1631,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425672</v>
+        <v>425686</v>
       </c>
       <c r="R11" t="n">
-        <v>7024137</v>
+        <v>7024135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134285118</v>
+        <v>134285116</v>
       </c>
       <c r="B12" t="n">
-        <v>92238</v>
+        <v>92406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1733,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425175</v>
+        <v>425632</v>
       </c>
       <c r="R12" t="n">
-        <v>7024293</v>
+        <v>7024316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134285115</v>
+        <v>134285122</v>
       </c>
       <c r="B13" t="n">
-        <v>92399</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1830,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425686</v>
+        <v>425710</v>
       </c>
       <c r="R13" t="n">
-        <v>7024135</v>
+        <v>7024267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134285116</v>
+        <v>134285123</v>
       </c>
       <c r="B14" t="n">
-        <v>92399</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425632</v>
+        <v>425272</v>
       </c>
       <c r="R14" t="n">
-        <v>7024316</v>
+        <v>7024531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134285123</v>
+        <v>134285124</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2024,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425272</v>
+        <v>425174</v>
       </c>
       <c r="R15" t="n">
-        <v>7024531</v>
+        <v>7024293</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,27 +2033,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285097</v>
+        <v>134285112</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2121,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425427</v>
+        <v>425364</v>
       </c>
       <c r="R16" t="n">
-        <v>7024497</v>
+        <v>7024553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,7 +2108,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285111</v>
+        <v>134285083</v>
       </c>
       <c r="B17" t="n">
-        <v>99210</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2223,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425183</v>
+        <v>425428</v>
       </c>
       <c r="R17" t="n">
-        <v>7024304</v>
+        <v>7024294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2285,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285083</v>
+        <v>134285084</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2320,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425428</v>
+        <v>425496</v>
       </c>
       <c r="R18" t="n">
-        <v>7024294</v>
+        <v>7024347</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2387,7 +2339,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285095</v>
+        <v>134285085</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2422,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425676</v>
+        <v>425469</v>
       </c>
       <c r="R19" t="n">
-        <v>7024309</v>
+        <v>7024326</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2414,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2489,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285103</v>
+        <v>134285086</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2518,16 +2470,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425095</v>
+        <v>425545</v>
       </c>
       <c r="R20" t="n">
-        <v>7024364</v>
+        <v>7024309</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,7 +2524,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,7 +2551,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134285094</v>
+        <v>134285087</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2626,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425647</v>
+        <v>425580</v>
       </c>
       <c r="R21" t="n">
-        <v>7024281</v>
+        <v>7024207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,7 +2626,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2693,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134285122</v>
+        <v>134285088</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2704,21 +2664,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425710</v>
+        <v>425672</v>
       </c>
       <c r="R22" t="n">
-        <v>7024267</v>
+        <v>7024137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,6 +2724,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2790,7 +2755,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134285096</v>
+        <v>134285089</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -2825,10 +2790,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425460</v>
+        <v>425778</v>
       </c>
       <c r="R23" t="n">
-        <v>7024452</v>
+        <v>7024318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2857,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134285102</v>
+        <v>134285090</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -2921,24 +2886,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425083</v>
+        <v>425660</v>
       </c>
       <c r="R24" t="n">
-        <v>7024539</v>
+        <v>7024220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2975,7 +2932,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3002,10 +2959,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134285120</v>
+        <v>134285091</v>
       </c>
       <c r="B25" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3013,21 +2970,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3037,10 +2994,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425614</v>
+        <v>425629</v>
       </c>
       <c r="R25" t="n">
-        <v>7024375</v>
+        <v>7024229</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,6 +3030,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (års) färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3099,7 +3061,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134285084</v>
+        <v>134285092</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3134,10 +3096,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425496</v>
+        <v>425635</v>
       </c>
       <c r="R26" t="n">
-        <v>7024347</v>
+        <v>7024244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,7 +3163,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285089</v>
+        <v>134285093</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3236,10 +3198,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>425778</v>
+        <v>425665</v>
       </c>
       <c r="R27" t="n">
-        <v>7024318</v>
+        <v>7024266</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,7 +3238,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3303,32 +3265,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134285113</v>
+        <v>134285094</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3338,10 +3300,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425631</v>
+        <v>425647</v>
       </c>
       <c r="R28" t="n">
-        <v>7024062</v>
+        <v>7024281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3374,6 +3336,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3400,10 +3367,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134285119</v>
+        <v>134285095</v>
       </c>
       <c r="B29" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3411,21 +3378,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3435,10 +3402,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425723</v>
+        <v>425676</v>
       </c>
       <c r="R29" t="n">
-        <v>7024299</v>
+        <v>7024309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3438,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3469,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134285117</v>
+        <v>134285096</v>
       </c>
       <c r="B30" t="n">
-        <v>92238</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3480,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3504,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425689</v>
+        <v>425460</v>
       </c>
       <c r="R30" t="n">
-        <v>7024137</v>
+        <v>7024452</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3540,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,10 +3571,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285121</v>
+        <v>134285097</v>
       </c>
       <c r="B31" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,21 +3582,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3629,10 +3606,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425149</v>
+        <v>425427</v>
       </c>
       <c r="R31" t="n">
-        <v>7024338</v>
+        <v>7024497</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3665,6 +3642,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3691,10 +3673,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134285082</v>
+        <v>134285098</v>
       </c>
       <c r="B32" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3702,21 +3684,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3726,10 +3708,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425684</v>
+        <v>425419</v>
       </c>
       <c r="R32" t="n">
-        <v>7024370</v>
+        <v>7024500</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3762,6 +3744,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3788,7 +3775,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134285085</v>
+        <v>134285100</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3823,10 +3810,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425469</v>
+        <v>425316</v>
       </c>
       <c r="R33" t="n">
-        <v>7024326</v>
+        <v>7024560</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3863,7 +3850,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3890,7 +3877,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134285092</v>
+        <v>134285101</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3925,10 +3912,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425635</v>
+        <v>425161</v>
       </c>
       <c r="R34" t="n">
-        <v>7024244</v>
+        <v>7024570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3965,7 +3952,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3992,7 +3979,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134285091</v>
+        <v>134285102</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4021,16 +4008,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425629</v>
+        <v>425083</v>
       </c>
       <c r="R35" t="n">
-        <v>7024229</v>
+        <v>7024539</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4067,7 +4062,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (års) färska och äldre</t>
+          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4094,32 +4089,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285125</v>
+        <v>134285103</v>
       </c>
       <c r="B36" t="n">
-        <v>92682</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4129,10 +4124,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425669</v>
+        <v>425095</v>
       </c>
       <c r="R36" t="n">
-        <v>7024226</v>
+        <v>7024364</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,6 +4160,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4191,32 +4191,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285124</v>
+        <v>134285111</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>99217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425174</v>
+        <v>425183</v>
       </c>
       <c r="R37" t="n">
-        <v>7024293</v>
+        <v>7024304</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285083</v>
+        <v>134285086</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2164,16 +2164,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425428</v>
+        <v>425545</v>
       </c>
       <c r="R17" t="n">
-        <v>7024294</v>
+        <v>7024309</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2218,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2237,7 +2245,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285084</v>
+        <v>134285102</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2266,16 +2274,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425496</v>
+        <v>425083</v>
       </c>
       <c r="R18" t="n">
-        <v>7024347</v>
+        <v>7024539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,7 +2328,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,32 +2355,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285085</v>
+        <v>134285111</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425469</v>
+        <v>425183</v>
       </c>
       <c r="R19" t="n">
-        <v>7024326</v>
+        <v>7024304</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,11 +2428,6 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2438,1853 +2449,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>134285086</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>425545</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7024309</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>134285087</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>425580</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7024207</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>134285088</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>425672</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7024137</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>134285089</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>425778</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7024318</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>134285090</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>425660</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7024220</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>134285091</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>425629</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7024229</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (års) färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>134285092</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>425635</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7024244</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>134285093</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>425665</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7024266</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>134285094</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>425647</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7024281</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>134285095</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>425676</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7024309</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>134285096</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>425460</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7024452</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>134285097</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>425427</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7024497</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>134285098</v>
-      </c>
-      <c r="B32" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>425419</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7024500</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>134285100</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>425316</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7024560</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>134285101</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>425161</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7024570</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>134285102</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>425083</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7024539</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>134285103</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>425095</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7024364</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>134285111</v>
-      </c>
-      <c r="B37" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Ällvåksviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>425183</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7024304</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285086</v>
+        <v>134285083</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2164,24 +2164,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425545</v>
+        <v>425428</v>
       </c>
       <c r="R17" t="n">
-        <v>7024309</v>
+        <v>7024294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2218,7 +2210,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2245,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285102</v>
+        <v>134285084</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2274,24 +2266,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ällvåksviken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425083</v>
+        <v>425496</v>
       </c>
       <c r="R18" t="n">
-        <v>7024539</v>
+        <v>7024347</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,7 +2312,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2355,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285111</v>
+        <v>134285085</v>
       </c>
       <c r="B19" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425183</v>
+        <v>425469</v>
       </c>
       <c r="R19" t="n">
-        <v>7024304</v>
+        <v>7024326</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2428,6 +2412,11 @@
           <t>2026-06-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2449,6 +2438,1853 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134285086</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>425545</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7024309</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål av färskare dato, ca 2 m upp i tajgagrantickerötad död gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134285087</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>425580</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7024207</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134285088</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>425672</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7024137</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134285089</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>425778</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7024318</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134285090</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>425660</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7024220</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134285091</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>425629</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7024229</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (års) färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134285092</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>425635</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7024244</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134285093</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>425665</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7024266</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134285094</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>425647</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7024281</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134285095</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>425676</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7024309</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134285096</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>425460</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7024452</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134285097</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>425427</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7024497</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134285098</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>425419</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7024500</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134285100</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>425316</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7024560</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134285101</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>425161</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7024570</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134285102</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>425083</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7024539</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, ca 4 m(resp 5,5m)upp i tajgagrantickerötad granhögstubbe.Dun på stammen intill hålet</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134285103</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>425095</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7024364</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134285111</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ällvåksviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>425183</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7024304</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285119</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285121</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285113</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285114</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285115</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285116</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285124</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285112</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285083</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285084</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285085</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2548,6 +2643,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285086</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285087</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2752,6 +2857,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285088</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285089</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2956,6 +3071,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285090</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3058,6 +3178,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285091</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3160,6 +3285,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285092</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285093</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3364,6 +3499,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285094</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3466,6 +3606,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285095</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3568,6 +3713,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285096</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285097</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3772,6 +3927,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285098</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3874,6 +4034,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3976,6 +4141,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285101</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4086,6 +4256,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285102</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4188,6 +4363,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285103</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4285,8 +4465,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285111</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23162-2026 artfynd.xlsx
+++ b/artfynd/A 23162-2026 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134285083</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>134285084</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>134285085</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>134285087</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>134285088</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>134285089</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>134285090</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>134285091</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>134285092</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>134285093</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>134285094</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>134285095</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>134285096</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>134285097</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>134285098</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>134285100</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>134285101</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>134285103</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
